--- a/data/HeureAudio.xlsx
+++ b/data/HeureAudio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationaudio/Shared Documents/Prestations Audio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AE05A5-6FB5-455D-8434-BC00F854579A}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9EEBF3-4883-4EC7-AEB9-7E4852A37833}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -336,6 +336,11 @@
             <v>0.43603577794754256</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.34714688905865365</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -443,6 +448,11 @@
             <v>0.24512908588995541</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.48749019700106655</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -550,6 +560,11 @@
             <v>0.88000000000000034</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.85916666666666708</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -657,6 +672,11 @@
             <v>0.52092171717171709</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.55286616161616153</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -764,6 +784,11 @@
             <v>0.48379079892826704</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.58517968781715601</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -871,6 +896,11 @@
             <v>0.24315390749601273</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.28809438368648893</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -978,6 +1008,11 @@
             <v>1.3256944444444458</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.4798611111111126</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1085,6 +1120,11 @@
             <v>0.90448976608187159</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.0301842105263161</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1192,6 +1232,11 @@
             <v>0.35263888888888895</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.12000000000000005</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0.50694444444444464</v>
@@ -1299,6 +1344,11 @@
             <v>0.27733389798607178</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.26969500909718291</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1406,6 +1456,11 @@
             <v>1.1570096618357484</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.0590929951690817</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1513,6 +1568,11 @@
             <v>0.63463852075744664</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.44158296520189111</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1620,6 +1680,11 @@
             <v>1.7883459595959601</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.8008459595959601</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1717,6 +1782,11 @@
             <v>0.97847222222222197</v>
           </cell>
         </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0.98819444444444415</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="14">
         <row r="2">
@@ -1757,6 +1827,11 @@
         <row r="11">
           <cell r="K11">
             <v>1.1737961455992147</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>1.1529628122658815</v>
           </cell>
         </row>
         <row r="19">
@@ -1869,8 +1944,8 @@
     <tableColumn id="6" xr3:uid="{D6979E67-6E41-4D87-8E2F-C77EC9B86F1C}" name="Avril" dataDxfId="21"/>
     <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="17"/>
     <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="16"/>
     <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="15"/>
@@ -3168,7 +3243,10 @@
         <f>[1]CARPENTIER!$K$11</f>
         <v>0.43603577794754256</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1">
+        <f>[1]CARPENTIER!$K$12</f>
+        <v>0.34714688905865365</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -3210,7 +3288,10 @@
         <f>[1]DAIX!$K$11</f>
         <v>0.24512908588995541</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1">
+        <f>[1]DAIX!$K$12</f>
+        <v>0.48749019700106655</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -3252,7 +3333,10 @@
         <f>'[1]DE LUCIA'!$K$11</f>
         <v>0.88000000000000034</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1">
+        <f>'[1]DE LUCIA'!$K$12</f>
+        <v>0.85916666666666708</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -3294,7 +3378,10 @@
         <f>[1]DENIS!$K$11</f>
         <v>0.52092171717171709</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1">
+        <f>[1]DENIS!$K$12</f>
+        <v>0.55286616161616153</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -3336,7 +3423,10 @@
         <f>[1]DEROY!$K$11</f>
         <v>0.48379079892826704</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="1">
+        <f>[1]DEROY!$K$12</f>
+        <v>0.58517968781715601</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -3378,7 +3468,10 @@
         <f>[1]DJEUKOUA!$K$11</f>
         <v>0.24315390749601273</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1">
+        <f>[1]DJEUKOUA!$K$12</f>
+        <v>0.28809438368648893</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -3420,7 +3513,10 @@
         <f>[1]HIDALGO!$K$11</f>
         <v>1.3256944444444458</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1">
+        <f>[1]HIDALGO!$K$12</f>
+        <v>1.4798611111111126</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -3462,7 +3558,10 @@
         <f>[1]LOGIST!$K$11</f>
         <v>0.90448976608187159</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1">
+        <f>[1]LOGIST!$K$12</f>
+        <v>1.0301842105263161</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -3504,7 +3603,10 @@
         <f>[1]MARTINOT!$K$11</f>
         <v>0.35263888888888895</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="1">
+        <f>[1]MARTINOT!$K$12</f>
+        <v>0.12000000000000005</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -3546,7 +3648,10 @@
         <f>[1]POURLIER!$K$11</f>
         <v>0.27733389798607178</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1">
+        <f>[1]POURLIER!$K$12</f>
+        <v>0.26969500909718291</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -3588,7 +3693,10 @@
         <f>[1]SEVRIN!$K$11</f>
         <v>1.1570096618357484</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1">
+        <f>[1]SEVRIN!$K$12</f>
+        <v>1.0590929951690817</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -3630,7 +3738,10 @@
         <f>[1]VANDENBOSCH!$K$11</f>
         <v>0.63463852075744664</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1">
+        <f>[1]VANDENBOSCH!$K$12</f>
+        <v>0.44158296520189111</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -3672,7 +3783,10 @@
         <f>[1]VILCHES!$K$11</f>
         <v>1.7883459595959601</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1">
+        <f>[1]VILCHES!$K$12</f>
+        <v>1.8008459595959601</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -3711,7 +3825,10 @@
         <f>[1]VITARELLA!$K$11</f>
         <v>0.97847222222222197</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1">
+        <f>[1]VITARELLA!$K$12</f>
+        <v>0.98819444444444415</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -3753,7 +3870,10 @@
         <f>[1]WAUTHELET!$K$11</f>
         <v>1.1737961455992147</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1">
+        <f>[1]WAUTHELET!$K$12</f>
+        <v>1.1529628122658815</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -3772,21 +3892,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D3876D2EFA434439C094FF2251913B9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d38a96a4d79b2def39fba2b13310c82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d07ca0ec-5157-41b5-8d0f-93bd9610df36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="650d5ff0aa0ee8df015896b7da2573e9" ns2:_="">
     <xsd:import namespace="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
@@ -3924,24 +4029,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A78B70F-238A-40F4-84C7-B703B6DF7536}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3957,4 +4060,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/HeureAudio.xlsx
+++ b/data/HeureAudio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fwb365.sharepoint.com/sites/CPM-Prestationaudio/Shared Documents/Prestations Audio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9EEBF3-4883-4EC7-AEB9-7E4852A37833}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="11_8BA3C09E2DF16CD648EA96253F05920B2FF8C28C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA7907BE-9F41-46F6-8974-12E77D5E1A0D}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025" sheetId="2" r:id="rId1"/>
@@ -333,12 +333,17 @@
         </row>
         <row r="11">
           <cell r="K11">
-            <v>0.43603577794754256</v>
+            <v>0.27909133350309812</v>
           </cell>
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0.34714688905865365</v>
+            <v>0.19020244461420921</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.1464524446142092</v>
           </cell>
         </row>
         <row r="19">
@@ -453,6 +458,11 @@
             <v>0.48749019700106655</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.66804575255662213</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -565,6 +575,11 @@
             <v>0.85916666666666708</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.76074494949494986</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -677,6 +692,11 @@
             <v>0.55286616161616153</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.25214646464646462</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -789,6 +809,11 @@
             <v>0.58517968781715601</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.3053185767060449</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -901,6 +926,11 @@
             <v>0.28809438368648893</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>-2.7768284347232108E-3</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1013,6 +1043,11 @@
             <v>1.4798611111111126</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.4527777777777793</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1125,6 +1160,11 @@
             <v>1.0301842105263161</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.1854872408293464</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1237,6 +1277,11 @@
             <v>0.12000000000000005</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.24500000000000005</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19">
             <v>0.50694444444444464</v>
@@ -1349,6 +1394,11 @@
             <v>0.26969500909718291</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.6460838979860718</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1461,6 +1511,11 @@
             <v>1.0590929951690817</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.1188985507246372</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1573,6 +1628,11 @@
             <v>0.44158296520189111</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.34271932883825473</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1685,6 +1745,11 @@
             <v>1.8008459595959601</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.9105681818181823</v>
+          </cell>
+        </row>
         <row r="19">
           <cell r="E19" t="str">
             <v xml:space="preserve"> </v>
@@ -1787,6 +1852,11 @@
             <v>0.98819444444444415</v>
           </cell>
         </row>
+        <row r="13">
+          <cell r="K13">
+            <v>1.2249999999999996</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="14">
         <row r="2">
@@ -1832,6 +1902,11 @@
         <row r="12">
           <cell r="K12">
             <v>1.1529628122658815</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>0.83629614559921484</v>
           </cell>
         </row>
         <row r="19">
@@ -1945,8 +2020,8 @@
     <tableColumn id="4" xr3:uid="{73890115-5FC3-4C52-9738-5535D8C89AA6}" name="Mai" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{C3AD0FE6-38FB-4AF2-A2FC-CD8C6AF1D34A}" name="Juin" dataDxfId="19"/>
     <tableColumn id="9" xr3:uid="{2CF88554-1C99-48F6-A58C-B366489DC66A}" name="Juillet" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{92839190-8610-4DAD-9F46-735A99F92CBC}" name="Août" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{29BF599E-3D07-4D08-9AF4-0E200B9474AF}" name="Septembre" dataDxfId="0"/>
     <tableColumn id="12" xr3:uid="{69B209A5-8270-436F-A131-3A88CE5DD18E}" name="Octobre" dataDxfId="16"/>
     <tableColumn id="13" xr3:uid="{5495805F-AD9C-4F16-87DB-C13BD64B4392}" name="Novembre" dataDxfId="15"/>
     <tableColumn id="14" xr3:uid="{4BC933CC-966E-4C7C-A940-6828309FC481}" name="Décembre" dataDxfId="14"/>
@@ -3241,13 +3316,16 @@
       </c>
       <c r="I2" s="1">
         <f>[1]CARPENTIER!$K$11</f>
-        <v>0.43603577794754256</v>
+        <v>0.27909133350309812</v>
       </c>
       <c r="J2" s="1">
         <f>[1]CARPENTIER!$K$12</f>
-        <v>0.34714688905865365</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>0.19020244461420921</v>
+      </c>
+      <c r="K2" s="1">
+        <f>[1]CARPENTIER!$K$13</f>
+        <v>0.1464524446142092</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -3292,7 +3370,10 @@
         <f>[1]DAIX!$K$12</f>
         <v>0.48749019700106655</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="K3" s="1">
+        <f>[1]DAIX!$K$13</f>
+        <v>0.66804575255662213</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -3337,7 +3418,10 @@
         <f>'[1]DE LUCIA'!$K$12</f>
         <v>0.85916666666666708</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1">
+        <f>'[1]DE LUCIA'!$K$13</f>
+        <v>0.76074494949494986</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -3382,7 +3466,10 @@
         <f>[1]DENIS!$K$12</f>
         <v>0.55286616161616153</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1">
+        <f>[1]DENIS!$K$13</f>
+        <v>0.25214646464646462</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -3427,7 +3514,10 @@
         <f>[1]DEROY!$K$12</f>
         <v>0.58517968781715601</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1">
+        <f>[1]DEROY!$K$13</f>
+        <v>0.3053185767060449</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -3472,7 +3562,10 @@
         <f>[1]DJEUKOUA!$K$12</f>
         <v>0.28809438368648893</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1">
+        <f>[1]DJEUKOUA!$K$13</f>
+        <v>-2.7768284347232108E-3</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
@@ -3517,7 +3610,10 @@
         <f>[1]HIDALGO!$K$12</f>
         <v>1.4798611111111126</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1">
+        <f>[1]HIDALGO!$K$13</f>
+        <v>1.4527777777777793</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -3562,7 +3658,10 @@
         <f>[1]LOGIST!$K$12</f>
         <v>1.0301842105263161</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1">
+        <f>[1]LOGIST!$K$13</f>
+        <v>1.1854872408293464</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -3607,7 +3706,10 @@
         <f>[1]MARTINOT!$K$12</f>
         <v>0.12000000000000005</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1">
+        <f>[1]MARTINOT!$K$13</f>
+        <v>0.24500000000000005</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -3652,7 +3754,10 @@
         <f>[1]POURLIER!$K$12</f>
         <v>0.26969500909718291</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <f>[1]POURLIER!$K$13</f>
+        <v>0.6460838979860718</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -3697,7 +3802,10 @@
         <f>[1]SEVRIN!$K$12</f>
         <v>1.0590929951690817</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1">
+        <f>[1]SEVRIN!$K$13</f>
+        <v>1.1188985507246372</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -3742,7 +3850,10 @@
         <f>[1]VANDENBOSCH!$K$12</f>
         <v>0.44158296520189111</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <f>[1]VANDENBOSCH!$K$13</f>
+        <v>0.34271932883825473</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -3787,7 +3898,10 @@
         <f>[1]VILCHES!$K$12</f>
         <v>1.8008459595959601</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1">
+        <f>[1]VILCHES!$K$13</f>
+        <v>1.9105681818181823</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -3829,7 +3943,10 @@
         <f>[1]VITARELLA!$K$12</f>
         <v>0.98819444444444415</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1">
+        <f>[1]VITARELLA!$K$13</f>
+        <v>1.2249999999999996</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -3874,7 +3991,10 @@
         <f>[1]WAUTHELET!$K$12</f>
         <v>1.1529628122658815</v>
       </c>
-      <c r="K16" s="1"/>
+      <c r="K16" s="1">
+        <f>[1]WAUTHELET!$K$13</f>
+        <v>0.83629614559921484</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -3892,6 +4012,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D3876D2EFA434439C094FF2251913B9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8d38a96a4d79b2def39fba2b13310c82">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d07ca0ec-5157-41b5-8d0f-93bd9610df36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="650d5ff0aa0ee8df015896b7da2573e9" ns2:_="">
     <xsd:import namespace="d07ca0ec-5157-41b5-8d0f-93bd9610df36"/>
@@ -4029,22 +4164,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A78B70F-238A-40F4-84C7-B703B6DF7536}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4060,21 +4197,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43162B4C-8036-4FD3-B02E-9FAB6E06A7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F5359EC-D85E-4EE8-994B-A84A38643895}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>